--- a/artfynd/A 14547-2026 artfynd.xlsx
+++ b/artfynd/A 14547-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132318230</v>
+        <v>132318237</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>78776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525336</v>
+        <v>525041</v>
       </c>
       <c r="R2" t="n">
-        <v>6877003</v>
+        <v>6876938</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132318231</v>
+        <v>132318258</v>
       </c>
       <c r="B3" t="n">
-        <v>79090</v>
+        <v>78776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,38 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Finneby, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525337</v>
+        <v>525042</v>
       </c>
       <c r="R3" t="n">
-        <v>6876997</v>
+        <v>6876940</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132318237</v>
+        <v>127414830</v>
       </c>
       <c r="B4" t="n">
-        <v>78735</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,13 +922,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525041</v>
+        <v>525337</v>
       </c>
       <c r="R4" t="n">
-        <v>6876938</v>
+        <v>6877052</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,12 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132318233</v>
+        <v>132318230</v>
       </c>
       <c r="B5" t="n">
-        <v>80437</v>
+        <v>79130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525245</v>
+        <v>525336</v>
       </c>
       <c r="R5" t="n">
-        <v>6876944</v>
+        <v>6877003</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132318259</v>
+        <v>127414828</v>
       </c>
       <c r="B6" t="n">
-        <v>80437</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,20 +1123,24 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Finneby, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525224</v>
+        <v>524934</v>
       </c>
       <c r="R6" t="n">
-        <v>6876931</v>
+        <v>6876998</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1201,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132318260</v>
+        <v>132318233</v>
       </c>
       <c r="B7" t="n">
-        <v>80437</v>
+        <v>80488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,17 +1229,21 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Finneby, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525244</v>
+        <v>525245</v>
       </c>
       <c r="R7" t="n">
-        <v>6876938</v>
+        <v>6876944</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132318258</v>
+        <v>132318234</v>
       </c>
       <c r="B8" t="n">
-        <v>78735</v>
+        <v>80488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1314,34 +1318,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Finneby, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525042</v>
+        <v>525219</v>
       </c>
       <c r="R8" t="n">
-        <v>6876940</v>
+        <v>6876929</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132318234</v>
+        <v>132318259</v>
       </c>
       <c r="B9" t="n">
-        <v>80437</v>
+        <v>80488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,21 +1441,17 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Finneby, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525219</v>
+        <v>525224</v>
       </c>
       <c r="R9" t="n">
-        <v>6876929</v>
+        <v>6876931</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132318235</v>
+        <v>132318260</v>
       </c>
       <c r="B10" t="n">
-        <v>79922</v>
+        <v>80488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,38 +1526,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Finneby, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525046</v>
+        <v>525244</v>
       </c>
       <c r="R10" t="n">
-        <v>6876937</v>
+        <v>6876938</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,6 +1614,218 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132318231</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Finneby, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>525337</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6876997</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132318235</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Finneby, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>525046</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6876937</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14547-2026 artfynd.xlsx
+++ b/artfynd/A 14547-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318237</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318258</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414830</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318230</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414828</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318233</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318234</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318259</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1614,6 +1659,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318260</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1720,6 +1770,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318231</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1826,8 +1881,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318235</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>